--- a/data/excel/equipments.xlsx
+++ b/data/excel/equipments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SunnydayBot\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA0D9E3-8945-45A0-A861-9319A5E96E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9D7C68-4665-460E-A2C5-58F1F1415FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
   <si>
     <t>id</t>
   </si>
@@ -338,6 +338,24 @@
   </si>
   <si>
     <t>frost</t>
+  </si>
+  <si>
+    <t>resist_bleed</t>
+  </si>
+  <si>
+    <t>resist_frost</t>
+  </si>
+  <si>
+    <t>resist_poison</t>
+  </si>
+  <si>
+    <t>resist_rot</t>
+  </si>
+  <si>
+    <t>resist_madness</t>
+  </si>
+  <si>
+    <t>resist_sleep</t>
   </si>
 </sst>
 </file>
@@ -373,8 +391,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,311 +1019,434 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14" style="3" customWidth="1"/>
+    <col min="4" max="15" width="8.88671875" style="3"/>
+    <col min="16" max="16" width="12" style="3" customWidth="1"/>
+    <col min="17" max="17" width="14" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="11.77734375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="15.109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="13.44140625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="40.44140625" style="3" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>8</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>4</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="3">
         <v>4</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <v>3</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
         <v>2</v>
       </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="O2" s="3">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>5</v>
+      </c>
+      <c r="R2" s="1">
+        <v>10</v>
+      </c>
+      <c r="S2" s="1">
+        <v>5</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <v>18</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <v>8</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>7</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>8</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="3">
         <v>3</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>8</v>
+      </c>
+      <c r="R3" s="1">
+        <v>10</v>
+      </c>
+      <c r="S3" s="1">
+        <v>10</v>
+      </c>
+      <c r="T3" s="1">
+        <v>5</v>
+      </c>
+      <c r="U3" s="1">
+        <v>5</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>7</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>16</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>6</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="3">
         <v>8</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
         <v>4</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
         <v>3</v>
       </c>
-      <c r="P4" t="s">
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>12</v>
+      </c>
+      <c r="R4" s="1">
+        <v>5</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1">
+        <v>15</v>
+      </c>
+      <c r="U4" s="1">
+        <v>5</v>
+      </c>
+      <c r="V4" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>5</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>6</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>14</v>
       </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
         <v>4</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
+      <c r="N5" s="3">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
         <v>2</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>5</v>
+      </c>
+      <c r="R5" s="1">
+        <v>8</v>
+      </c>
+      <c r="S5" s="1">
+        <v>15</v>
+      </c>
+      <c r="T5" s="1">
+        <v>10</v>
+      </c>
+      <c r="U5" s="1">
+        <v>12</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>28</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>12</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>8</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>10</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
         <v>10</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="3">
         <v>5</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="3">
         <v>3</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
         <v>-2</v>
       </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="O6" s="3">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1">
+        <v>12</v>
+      </c>
+      <c r="S6" s="1">
+        <v>12</v>
+      </c>
+      <c r="T6" s="1">
+        <v>8</v>
+      </c>
+      <c r="U6" s="1">
+        <v>5</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>63</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
